--- a/iteration_data.xlsx
+++ b/iteration_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,6 +457,40 @@
         </is>
       </c>
       <c r="C2" t="inlineStr">
+        <is>
+          <t>Sunday, 22 March, 2026, week 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-03-22 20:45:09</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>20:45:07</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Sunday, 22 March, 2026, week 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-03-22 20:46:59</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>20:46:57</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>Sunday, 22 March, 2026, week 12</t>
         </is>
